--- a/mappingCorps/ig/FRLaboratoryResultClinicalElementLMCDAFHIR.xlsx
+++ b/mappingCorps/ig/FRLaboratoryResultClinicalElementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:18:14+00:00</t>
+    <t>2026-08-05T09:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
